--- a/estatemaster-agent/setup/KINAN_control_workbook_template.xlsx
+++ b/estatemaster-agent/setup/KINAN_control_workbook_template.xlsx
@@ -10,8 +10,9 @@
     <sheet name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Project" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mapping" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Checks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mapping" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Checks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -539,6 +540,20 @@
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Lines this project does not use: leave column E blank and put N/A in column H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Every other assumption goes on the Lines sheet: no limit, one row per input, id L0001, L0002, … Add rows at the</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   bottom only, link column E in EstateMaster, then put Y in column J. Unlinked lines are never written by the runner.</t>
         </is>
       </c>
     </row>
@@ -1489,6 +1504,706 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J203"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model lines: every other assumption, no limit. Add rows at the bottom only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>One row per EstateMaster input. Id in column A (L0001, L0002, …), unique and never reused. Column E is what EstateMaster reads; link it once, then put Y in column J.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Source in EstateMaster export</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Mapped by</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed (Y/N/N/A)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Linked in EstateMaster (Y/N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="E4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="E12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="H4:H200000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J4:J200000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2437,13 +3152,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2539,8 +3254,30 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Model lines (sheet Lines)</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>COUNTA(Lines!A4:A200000)</f>
+        <v/>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Model lines linked in EstateMaster</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <f>COUNTIF(Lines!J4:J200000,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Full validation (units, ranges, duplicates): py runner/control_check.py &lt;file&gt;</t>
         </is>
